--- a/Versão5/VEGE/Ontologia_VEGET.xlsx
+++ b/Versão5/VEGE/Ontologia_VEGET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VEGE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D552EDB-B37A-476F-A787-BDD67AEAB79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774F1A6A-0F47-4BF1-BD43-4C1024D15E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -3913,9 +3913,6 @@
     <t>"Corypha umbraculifera"</t>
   </si>
   <si>
-    <t>"Tronco esguio com folhas palmadas em leque, com até 5 m de envergadura. Também é chamada de palmeira-parasol ou palma de Ceilão. Após floração deve ser monitorada por especialistas, pois pode apresentar risco de queda"</t>
-  </si>
-  <si>
     <t>"1 até 3 m"</t>
   </si>
   <si>
@@ -3925,9 +3922,6 @@
     <t>"Ornamental em parques urbanos"</t>
   </si>
   <si>
-    <t>"Monocárpica, floresce uma única vez após 60 a 80. Após a floração, entra em senescência e as folhas secam o tronco perde vigor e a planta morre. Nessa época, produz milhões de frutos esféricos. O evento pode ser apreciado no aterro do Flamengo em Novembro de 2025, pois as palmeiras plantadas há mais de 60 anos pelo paisagista Roberto Burle Marx finalmente revelaram o seu espetáculo mais grandioso"</t>
-  </si>
-  <si>
     <t>"Árvore nativa do Brasil de grande porte (até 30 m), com raízes aéreas que estrangulam outras árvores, daí o nome 'mata-pau'. Folhas grandes, ovais, com nervuras marcadas. produzem látex branco"</t>
   </si>
   <si>
@@ -4064,6 +4058,12 @@
   </si>
   <si>
     <t>diâmetro.máximo.da.copa</t>
+  </si>
+  <si>
+    <t>"Tronco esguio com folhas palmadas em leque, com até 5 m de envergadura. Também é chamada de palmeira-parasol ou palma de Ceilão. Após floração a planta morre durante o ano seguinte"</t>
+  </si>
+  <si>
+    <t>"Monocárpica, floresce uma única vez após 60 a 80. Após a floração, entra em senescência e as folhas secam o tronco perde vigor e a planta morre. Nessa época, produz milhões de frutos esféricos. O evento pode ser apreciado no aterro do Flamengo em Novembro de 2025, quando as palmeiras plantadas há mais de 60 anos pelo paisagista Roberto Burle Marx finalmente floreceram."</t>
   </si>
 </sst>
 </file>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B18" s="71">
         <f ca="1">NOW()</f>
-        <v>46157.76692037037</v>
+        <v>46164.480950810183</v>
       </c>
       <c r="C18" s="93" t="s">
         <v>1266</v>
@@ -5829,7 +5829,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="104" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C2" s="105" t="s">
         <v>78</v>
@@ -5838,10 +5838,10 @@
         <v>77</v>
       </c>
       <c r="E2" s="104" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F2" s="105" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="G2" s="106" t="s">
         <v>1</v>
@@ -5875,10 +5875,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="26" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="R2" s="27" t="s">
         <v>1</v>
@@ -5896,7 +5896,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W2" s="110" t="str">
         <f>CONCATENATE("Key-VEG-",A2)</f>
@@ -5921,7 +5921,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="104" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C3" s="105" t="s">
         <v>78</v>
@@ -5930,10 +5930,10 @@
         <v>77</v>
       </c>
       <c r="E3" s="104" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="F3" s="105" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="G3" s="106" t="s">
         <v>1</v>
@@ -5967,10 +5967,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="26" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="R3" s="27" t="s">
         <v>1</v>
@@ -5988,7 +5988,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W3" s="110" t="str">
         <f t="shared" ref="W3:W52" si="4">CONCATENATE("Key-VEG-",A3)</f>
@@ -6013,7 +6013,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C4" s="105" t="s">
         <v>78</v>
@@ -6022,10 +6022,10 @@
         <v>77</v>
       </c>
       <c r="E4" s="104" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="F4" s="105" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G4" s="106" t="s">
         <v>1</v>
@@ -6059,10 +6059,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q4" s="26" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="R4" s="27" t="s">
         <v>1</v>
@@ -6080,7 +6080,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W4" s="110" t="str">
         <f t="shared" si="4"/>
@@ -6105,7 +6105,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="104" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C5" s="105" t="s">
         <v>78</v>
@@ -6114,10 +6114,10 @@
         <v>77</v>
       </c>
       <c r="E5" s="104" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="F5" s="105" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="G5" s="106" t="s">
         <v>1</v>
@@ -6151,10 +6151,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="26" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="R5" s="27" t="s">
         <v>1</v>
@@ -6172,7 +6172,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W5" s="110" t="str">
         <f t="shared" si="4"/>
@@ -6197,7 +6197,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C6" s="105" t="s">
         <v>78</v>
@@ -6206,10 +6206,10 @@
         <v>77</v>
       </c>
       <c r="E6" s="104" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="F6" s="105" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="G6" s="106" t="s">
         <v>1</v>
@@ -6243,10 +6243,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="26" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="R6" s="27" t="s">
         <v>1</v>
@@ -6264,7 +6264,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W6" s="110" t="str">
         <f t="shared" si="4"/>
@@ -6356,20 +6356,20 @@
         <v>Flora</v>
       </c>
       <c r="V7" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W7" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-7</v>
       </c>
       <c r="X7" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y7" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z7" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y7" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z7" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA7" s="26" t="str">
         <f t="shared" ref="AA7:AA52" si="12">_xlfn.TRANSLATE(P7,"pt","en")</f>
@@ -6448,20 +6448,20 @@
         <v>Flora</v>
       </c>
       <c r="V8" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W8" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-8</v>
       </c>
       <c r="X8" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y8" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z8" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y8" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z8" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA8" s="26" t="str">
         <f t="shared" si="12"/>
@@ -6540,20 +6540,20 @@
         <v>Flora</v>
       </c>
       <c r="V9" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W9" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-9</v>
       </c>
       <c r="X9" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y9" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z9" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y9" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z9" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA9" s="26" t="str">
         <f t="shared" si="12"/>
@@ -6632,20 +6632,20 @@
         <v>Flora</v>
       </c>
       <c r="V10" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W10" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-10</v>
       </c>
       <c r="X10" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y10" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z10" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y10" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z10" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA10" s="26" t="str">
         <f t="shared" si="12"/>
@@ -6724,20 +6724,20 @@
         <v>Flora</v>
       </c>
       <c r="V11" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W11" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-11</v>
       </c>
       <c r="X11" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y11" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z11" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y11" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z11" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA11" s="26" t="str">
         <f t="shared" si="12"/>
@@ -6816,20 +6816,20 @@
         <v>Flora</v>
       </c>
       <c r="V12" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W12" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-12</v>
       </c>
       <c r="X12" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y12" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z12" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y12" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z12" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA12" s="26" t="str">
         <f t="shared" si="12"/>
@@ -6908,20 +6908,20 @@
         <v>Flora</v>
       </c>
       <c r="V13" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W13" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-13</v>
       </c>
       <c r="X13" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y13" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z13" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y13" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z13" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA13" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7000,20 +7000,20 @@
         <v>Flora</v>
       </c>
       <c r="V14" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W14" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-14</v>
       </c>
       <c r="X14" s="26" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="Y14" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z14" s="28" t="s">
         <v>1304</v>
-      </c>
-      <c r="Z14" s="28" t="s">
-        <v>1306</v>
       </c>
       <c r="AA14" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7092,20 +7092,20 @@
         <v>Flora</v>
       </c>
       <c r="V15" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W15" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-15</v>
       </c>
       <c r="X15" s="26" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="Y15" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z15" s="28" t="s">
         <v>1304</v>
-      </c>
-      <c r="Z15" s="28" t="s">
-        <v>1306</v>
       </c>
       <c r="AA15" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7184,20 +7184,20 @@
         <v>Flora</v>
       </c>
       <c r="V16" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W16" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-16</v>
       </c>
       <c r="X16" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y16" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z16" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y16" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z16" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA16" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7276,20 +7276,20 @@
         <v>Flora</v>
       </c>
       <c r="V17" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W17" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-17</v>
       </c>
       <c r="X17" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y17" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z17" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y17" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z17" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA17" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7368,20 +7368,20 @@
         <v>Flora</v>
       </c>
       <c r="V18" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W18" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-18</v>
       </c>
       <c r="X18" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y18" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z18" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y18" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z18" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA18" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7460,20 +7460,20 @@
         <v>Flora</v>
       </c>
       <c r="V19" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W19" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-19</v>
       </c>
       <c r="X19" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y19" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z19" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y19" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z19" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA19" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7552,20 +7552,20 @@
         <v>Fungos</v>
       </c>
       <c r="V20" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W20" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-20</v>
       </c>
       <c r="X20" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y20" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z20" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y20" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z20" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA20" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7644,20 +7644,20 @@
         <v>Conservação</v>
       </c>
       <c r="V21" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W21" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-21</v>
       </c>
       <c r="X21" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y21" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z21" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA21" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7736,20 +7736,20 @@
         <v>Conservação</v>
       </c>
       <c r="V22" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W22" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-22</v>
       </c>
       <c r="X22" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y22" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z22" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA22" s="26" t="str">
         <f t="shared" si="12"/>
@@ -7807,10 +7807,10 @@
         <v>Conservação Mineral</v>
       </c>
       <c r="P23" s="29" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="Q23" s="29" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="R23" s="27" t="s">
         <v>1</v>
@@ -7828,20 +7828,20 @@
         <v>Conservação</v>
       </c>
       <c r="V23" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W23" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-23</v>
       </c>
       <c r="X23" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y23" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z23" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA23" s="26" t="str">
         <f t="shared" ref="AA23" si="62">_xlfn.TRANSLATE(P23,"pt","en")</f>
@@ -7865,7 +7865,7 @@
         <v>862</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="G24" s="106" t="s">
         <v>1</v>
@@ -7920,20 +7920,20 @@
         <v>Conservação</v>
       </c>
       <c r="V24" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W24" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-24</v>
       </c>
       <c r="X24" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y24" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z24" s="28" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="AA24" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8012,20 +8012,20 @@
         <v>Captura de CO2</v>
       </c>
       <c r="V25" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W25" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-25</v>
       </c>
       <c r="X25" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y25" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z25" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA25" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8104,20 +8104,20 @@
         <v>Captura de CO2</v>
       </c>
       <c r="V26" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W26" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-26</v>
       </c>
       <c r="X26" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y26" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z26" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA26" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8196,20 +8196,20 @@
         <v>Tipos de Solo</v>
       </c>
       <c r="V27" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W27" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-27</v>
       </c>
       <c r="X27" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="Y27" s="28" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="Z27" s="28" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="AA27" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8288,20 +8288,20 @@
         <v>Tipos de Solo</v>
       </c>
       <c r="V28" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W28" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-28</v>
       </c>
       <c r="X28" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="Y28" s="28" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="Z28" s="28" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="AA28" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8380,20 +8380,20 @@
         <v>Tipos de Solo</v>
       </c>
       <c r="V29" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W29" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-29</v>
       </c>
       <c r="X29" s="26" t="s">
+        <v>1306</v>
+      </c>
+      <c r="Y29" s="28" t="s">
+        <v>1307</v>
+      </c>
+      <c r="Z29" s="28" t="s">
         <v>1308</v>
-      </c>
-      <c r="Y29" s="28" t="s">
-        <v>1309</v>
-      </c>
-      <c r="Z29" s="28" t="s">
-        <v>1310</v>
       </c>
       <c r="AA29" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8472,20 +8472,20 @@
         <v>Exposição Solar</v>
       </c>
       <c r="V30" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W30" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-30</v>
       </c>
       <c r="X30" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y30" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z30" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA30" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8564,20 +8564,20 @@
         <v>Exposição Solar</v>
       </c>
       <c r="V31" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W31" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-31</v>
       </c>
       <c r="X31" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y31" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z31" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA31" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8656,20 +8656,20 @@
         <v>Exposição Solar</v>
       </c>
       <c r="V32" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W32" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-32</v>
       </c>
       <c r="X32" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y32" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z32" s="28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AA32" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8748,20 +8748,20 @@
         <v>Plantações</v>
       </c>
       <c r="V33" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W33" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-33</v>
       </c>
       <c r="X33" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y33" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z33" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y33" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z33" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA33" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8840,20 +8840,20 @@
         <v>Plantações</v>
       </c>
       <c r="V34" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W34" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-34</v>
       </c>
       <c r="X34" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y34" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z34" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y34" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z34" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA34" s="26" t="str">
         <f t="shared" si="12"/>
@@ -8932,20 +8932,20 @@
         <v>Plantações</v>
       </c>
       <c r="V35" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W35" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-35</v>
       </c>
       <c r="X35" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y35" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z35" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y35" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z35" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA35" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9024,20 +9024,20 @@
         <v>Plantações</v>
       </c>
       <c r="V36" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W36" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-36</v>
       </c>
       <c r="X36" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y36" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z36" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y36" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z36" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA36" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9116,20 +9116,20 @@
         <v>Plantações</v>
       </c>
       <c r="V37" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W37" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-37</v>
       </c>
       <c r="X37" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y37" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z37" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y37" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z37" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA37" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9208,20 +9208,20 @@
         <v>Plantações</v>
       </c>
       <c r="V38" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W38" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-38</v>
       </c>
       <c r="X38" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y38" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z38" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y38" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z38" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA38" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9300,20 +9300,20 @@
         <v>Plantações</v>
       </c>
       <c r="V39" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W39" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-39</v>
       </c>
       <c r="X39" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y39" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z39" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y39" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z39" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA39" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9392,20 +9392,20 @@
         <v>Plantações</v>
       </c>
       <c r="V40" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W40" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-40</v>
       </c>
       <c r="X40" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y40" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z40" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y40" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z40" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA40" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9484,20 +9484,20 @@
         <v>Tipos de Jardim</v>
       </c>
       <c r="V41" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W41" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-41</v>
       </c>
       <c r="X41" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y41" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z41" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA41" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9576,20 +9576,20 @@
         <v>Tipos de Jardim</v>
       </c>
       <c r="V42" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W42" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-42</v>
       </c>
       <c r="X42" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y42" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z42" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA42" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9668,20 +9668,20 @@
         <v>Tipos de Jardim</v>
       </c>
       <c r="V43" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W43" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-43</v>
       </c>
       <c r="X43" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y43" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z43" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA43" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9760,20 +9760,20 @@
         <v>Tipos de Jardim</v>
       </c>
       <c r="V44" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W44" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-44</v>
       </c>
       <c r="X44" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y44" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z44" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA44" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9852,20 +9852,20 @@
         <v>Elementos Hídricos</v>
       </c>
       <c r="V45" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W45" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-45</v>
       </c>
       <c r="X45" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y45" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z45" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA45" s="26" t="str">
         <f t="shared" si="12"/>
@@ -9944,20 +9944,20 @@
         <v>Elementos Hídricos</v>
       </c>
       <c r="V46" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W46" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-46</v>
       </c>
       <c r="X46" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y46" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z46" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA46" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10036,20 +10036,20 @@
         <v>Elementos Hídricos</v>
       </c>
       <c r="V47" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W47" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-47</v>
       </c>
       <c r="X47" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y47" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Z47" s="28" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="AA47" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10128,20 +10128,20 @@
         <v>Elementos Verdes</v>
       </c>
       <c r="V48" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W48" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-48</v>
       </c>
       <c r="X48" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y48" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z48" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y48" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z48" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA48" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10220,20 +10220,20 @@
         <v>Elementos Verdes</v>
       </c>
       <c r="V49" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W49" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-49</v>
       </c>
       <c r="X49" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y49" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z49" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y49" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z49" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA49" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10312,20 +10312,20 @@
         <v>Elementos Verdes</v>
       </c>
       <c r="V50" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W50" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-50</v>
       </c>
       <c r="X50" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="Y50" s="28" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="Z50" s="28" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="AA50" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10404,20 +10404,20 @@
         <v>Elementos Secos</v>
       </c>
       <c r="V51" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W51" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-51</v>
       </c>
       <c r="X51" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="Y51" s="28" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="Z51" s="28" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="AA51" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10496,20 +10496,20 @@
         <v>Ordem Botânica</v>
       </c>
       <c r="V52" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="W52" s="110" t="str">
         <f t="shared" si="4"/>
         <v>Key-VEG-52</v>
       </c>
       <c r="X52" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="Y52" s="28" t="s">
+        <v>1302</v>
+      </c>
+      <c r="Z52" s="28" t="s">
         <v>1303</v>
-      </c>
-      <c r="Y52" s="28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="Z52" s="28" t="s">
-        <v>1305</v>
       </c>
       <c r="AA52" s="26" t="str">
         <f t="shared" si="12"/>
@@ -10933,7 +10933,7 @@
     <col min="50" max="16384" width="9.23046875" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="16.850000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:51" ht="15.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -11235,10 +11235,10 @@
         <v>1276</v>
       </c>
       <c r="AX2" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY2" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="3" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11390,10 +11390,10 @@
         <v>1276</v>
       </c>
       <c r="AX3" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY3" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="4" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11545,10 +11545,10 @@
         <v>1276</v>
       </c>
       <c r="AX4" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY4" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11700,10 +11700,10 @@
         <v>1276</v>
       </c>
       <c r="AX5" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY5" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="6" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11855,10 +11855,10 @@
         <v>1276</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY6" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12010,10 +12010,10 @@
         <v>1276</v>
       </c>
       <c r="AX7" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY7" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="8" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12165,10 +12165,10 @@
         <v>1276</v>
       </c>
       <c r="AX8" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY8" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="9" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12320,10 +12320,10 @@
         <v>1276</v>
       </c>
       <c r="AX9" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY9" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="10" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12475,10 +12475,10 @@
         <v>1276</v>
       </c>
       <c r="AX10" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY10" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="11" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12630,10 +12630,10 @@
         <v>1276</v>
       </c>
       <c r="AX11" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY11" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="12" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12785,10 +12785,10 @@
         <v>1276</v>
       </c>
       <c r="AX12" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY12" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="13" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12940,10 +12940,10 @@
         <v>1276</v>
       </c>
       <c r="AX13" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY13" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="14" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13095,10 +13095,10 @@
         <v>1276</v>
       </c>
       <c r="AX14" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY14" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="15" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13250,10 +13250,10 @@
         <v>1276</v>
       </c>
       <c r="AX15" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY15" s="31" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="16" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13405,10 +13405,10 @@
         <v>1276</v>
       </c>
       <c r="AX16" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY16" s="31" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="17" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13560,10 +13560,10 @@
         <v>1276</v>
       </c>
       <c r="AX17" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY17" s="31" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="18" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13715,10 +13715,10 @@
         <v>1276</v>
       </c>
       <c r="AX18" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY18" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="19" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13870,10 +13870,10 @@
         <v>1276</v>
       </c>
       <c r="AX19" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY19" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="20" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14025,10 +14025,10 @@
         <v>1276</v>
       </c>
       <c r="AX20" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY20" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="21" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14180,10 +14180,10 @@
         <v>1276</v>
       </c>
       <c r="AX21" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY21" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="22" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14335,10 +14335,10 @@
         <v>1276</v>
       </c>
       <c r="AX22" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY22" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="23" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14490,10 +14490,10 @@
         <v>1276</v>
       </c>
       <c r="AX23" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY23" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="24" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14645,10 +14645,10 @@
         <v>1276</v>
       </c>
       <c r="AX24" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY24" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="25" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14800,10 +14800,10 @@
         <v>1276</v>
       </c>
       <c r="AX25" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY25" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="26" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -14955,10 +14955,10 @@
         <v>1276</v>
       </c>
       <c r="AX26" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY26" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="27" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15110,10 +15110,10 @@
         <v>1276</v>
       </c>
       <c r="AX27" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY27" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="28" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15265,10 +15265,10 @@
         <v>1276</v>
       </c>
       <c r="AX28" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY28" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="29" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15420,10 +15420,10 @@
         <v>1276</v>
       </c>
       <c r="AX29" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY29" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="30" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15575,10 +15575,10 @@
         <v>1276</v>
       </c>
       <c r="AX30" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY30" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="31" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15730,10 +15730,10 @@
         <v>1276</v>
       </c>
       <c r="AX31" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY31" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="32" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15885,10 +15885,10 @@
         <v>1276</v>
       </c>
       <c r="AX32" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY32" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="33" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16040,10 +16040,10 @@
         <v>1276</v>
       </c>
       <c r="AX33" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY33" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="34" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16195,10 +16195,10 @@
         <v>1276</v>
       </c>
       <c r="AX34" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY34" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="35" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16350,10 +16350,10 @@
         <v>1276</v>
       </c>
       <c r="AX35" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY35" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16505,10 +16505,10 @@
         <v>1276</v>
       </c>
       <c r="AX36" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY36" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="37" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16660,10 +16660,10 @@
         <v>1276</v>
       </c>
       <c r="AX37" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY37" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="38" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16815,10 +16815,10 @@
         <v>1276</v>
       </c>
       <c r="AX38" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY38" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="39" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -16970,10 +16970,10 @@
         <v>1276</v>
       </c>
       <c r="AX39" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY39" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="40" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17125,10 +17125,10 @@
         <v>1276</v>
       </c>
       <c r="AX40" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY40" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="41" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17247,7 +17247,7 @@
         <v>187</v>
       </c>
       <c r="AM41" s="44" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="AN41" s="33" t="s">
         <v>1</v>
@@ -17280,10 +17280,10 @@
         <v>1276</v>
       </c>
       <c r="AX41" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY41" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="42" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17435,10 +17435,10 @@
         <v>1276</v>
       </c>
       <c r="AX42" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY42" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17590,10 +17590,10 @@
         <v>1276</v>
       </c>
       <c r="AX43" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY43" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17745,10 +17745,10 @@
         <v>1276</v>
       </c>
       <c r="AX44" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY44" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -17900,10 +17900,10 @@
         <v>1276</v>
       </c>
       <c r="AX45" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY45" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18055,10 +18055,10 @@
         <v>1276</v>
       </c>
       <c r="AX46" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY46" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="47" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18210,10 +18210,10 @@
         <v>1276</v>
       </c>
       <c r="AX47" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY47" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18365,10 +18365,10 @@
         <v>1276</v>
       </c>
       <c r="AX48" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY48" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="49" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18520,10 +18520,10 @@
         <v>1276</v>
       </c>
       <c r="AX49" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY49" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="50" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18675,10 +18675,10 @@
         <v>1276</v>
       </c>
       <c r="AX50" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY50" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="51" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18830,10 +18830,10 @@
         <v>1276</v>
       </c>
       <c r="AX51" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY51" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="52" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -18985,10 +18985,10 @@
         <v>1276</v>
       </c>
       <c r="AX52" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY52" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="53" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19140,10 +19140,10 @@
         <v>1276</v>
       </c>
       <c r="AX53" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY53" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="54" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19295,10 +19295,10 @@
         <v>1276</v>
       </c>
       <c r="AX54" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY54" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="55" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19450,10 +19450,10 @@
         <v>1276</v>
       </c>
       <c r="AX55" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY55" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="56" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19605,10 +19605,10 @@
         <v>1276</v>
       </c>
       <c r="AX56" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY56" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="57" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19760,10 +19760,10 @@
         <v>1276</v>
       </c>
       <c r="AX57" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY57" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="58" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -19915,10 +19915,10 @@
         <v>1276</v>
       </c>
       <c r="AX58" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY58" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="59" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20070,10 +20070,10 @@
         <v>1276</v>
       </c>
       <c r="AX59" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY59" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="60" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20225,10 +20225,10 @@
         <v>1276</v>
       </c>
       <c r="AX60" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY60" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="61" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20380,10 +20380,10 @@
         <v>1276</v>
       </c>
       <c r="AX61" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY61" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="62" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20535,10 +20535,10 @@
         <v>1276</v>
       </c>
       <c r="AX62" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY62" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="63" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20690,10 +20690,10 @@
         <v>1276</v>
       </c>
       <c r="AX63" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY63" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="64" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -20845,10 +20845,10 @@
         <v>1276</v>
       </c>
       <c r="AX64" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY64" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="65" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21000,10 +21000,10 @@
         <v>1276</v>
       </c>
       <c r="AX65" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY65" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="66" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21155,10 +21155,10 @@
         <v>1276</v>
       </c>
       <c r="AX66" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY66" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="67" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21310,10 +21310,10 @@
         <v>1276</v>
       </c>
       <c r="AX67" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY67" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="68" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21465,10 +21465,10 @@
         <v>1276</v>
       </c>
       <c r="AX68" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY68" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="69" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21620,10 +21620,10 @@
         <v>1276</v>
       </c>
       <c r="AX69" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY69" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="70" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21775,10 +21775,10 @@
         <v>1276</v>
       </c>
       <c r="AX70" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY70" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="71" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -21930,10 +21930,10 @@
         <v>1276</v>
       </c>
       <c r="AX71" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY71" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="72" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22085,10 +22085,10 @@
         <v>1276</v>
       </c>
       <c r="AX72" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY72" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="73" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22240,10 +22240,10 @@
         <v>1276</v>
       </c>
       <c r="AX73" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY73" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="74" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22395,10 +22395,10 @@
         <v>1276</v>
       </c>
       <c r="AX74" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY74" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="75" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22550,10 +22550,10 @@
         <v>1276</v>
       </c>
       <c r="AX75" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY75" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="76" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22705,10 +22705,10 @@
         <v>1276</v>
       </c>
       <c r="AX76" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY76" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="77" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -22860,10 +22860,10 @@
         <v>1276</v>
       </c>
       <c r="AX77" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY77" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="78" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23015,10 +23015,10 @@
         <v>1276</v>
       </c>
       <c r="AX78" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY78" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="79" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23170,10 +23170,10 @@
         <v>1276</v>
       </c>
       <c r="AX79" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY79" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="80" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23325,10 +23325,10 @@
         <v>1276</v>
       </c>
       <c r="AX80" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY80" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="81" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23480,10 +23480,10 @@
         <v>1276</v>
       </c>
       <c r="AX81" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY81" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="82" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23635,10 +23635,10 @@
         <v>1276</v>
       </c>
       <c r="AX82" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY82" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="83" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23790,10 +23790,10 @@
         <v>1276</v>
       </c>
       <c r="AX83" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY83" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="84" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -23945,10 +23945,10 @@
         <v>1276</v>
       </c>
       <c r="AX84" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY84" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="85" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24100,10 +24100,10 @@
         <v>1276</v>
       </c>
       <c r="AX85" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY85" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="86" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24255,10 +24255,10 @@
         <v>1276</v>
       </c>
       <c r="AX86" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY86" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="87" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24410,10 +24410,10 @@
         <v>1276</v>
       </c>
       <c r="AX87" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY87" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="88" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24565,10 +24565,10 @@
         <v>1276</v>
       </c>
       <c r="AX88" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY88" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="89" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24720,10 +24720,10 @@
         <v>1276</v>
       </c>
       <c r="AX89" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY89" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="90" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -24875,10 +24875,10 @@
         <v>1276</v>
       </c>
       <c r="AX90" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY90" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="91" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25030,10 +25030,10 @@
         <v>1276</v>
       </c>
       <c r="AX91" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY91" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="92" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25185,10 +25185,10 @@
         <v>1276</v>
       </c>
       <c r="AX92" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY92" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="93" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25340,10 +25340,10 @@
         <v>1276</v>
       </c>
       <c r="AX93" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY93" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="94" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25495,10 +25495,10 @@
         <v>1276</v>
       </c>
       <c r="AX94" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY94" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="95" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25650,10 +25650,10 @@
         <v>1276</v>
       </c>
       <c r="AX95" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY95" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="96" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25805,10 +25805,10 @@
         <v>1276</v>
       </c>
       <c r="AX96" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY96" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="97" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -25960,10 +25960,10 @@
         <v>1276</v>
       </c>
       <c r="AX97" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY97" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="98" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26115,10 +26115,10 @@
         <v>1276</v>
       </c>
       <c r="AX98" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY98" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="99" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26270,10 +26270,10 @@
         <v>1276</v>
       </c>
       <c r="AX99" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY99" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="100" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26425,10 +26425,10 @@
         <v>1276</v>
       </c>
       <c r="AX100" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY100" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="101" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26580,10 +26580,10 @@
         <v>1276</v>
       </c>
       <c r="AX101" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY101" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="102" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26735,10 +26735,10 @@
         <v>1276</v>
       </c>
       <c r="AX102" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY102" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="103" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -26890,10 +26890,10 @@
         <v>1276</v>
       </c>
       <c r="AX103" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY103" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="104" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27045,10 +27045,10 @@
         <v>1276</v>
       </c>
       <c r="AX104" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY104" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="105" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27200,10 +27200,10 @@
         <v>1276</v>
       </c>
       <c r="AX105" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY105" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="106" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27355,10 +27355,10 @@
         <v>1276</v>
       </c>
       <c r="AX106" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY106" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="107" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27510,10 +27510,10 @@
         <v>1276</v>
       </c>
       <c r="AX107" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY107" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="108" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27665,10 +27665,10 @@
         <v>1276</v>
       </c>
       <c r="AX108" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY108" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="109" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27724,19 +27724,19 @@
         <v>683</v>
       </c>
       <c r="R109" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S109" s="49">
         <v>0</v>
       </c>
       <c r="T109" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U109" s="55">
         <v>0</v>
       </c>
       <c r="V109" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W109" s="55">
         <v>0</v>
@@ -27820,10 +27820,10 @@
         <v>1276</v>
       </c>
       <c r="AX109" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY109" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="110" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -27879,19 +27879,19 @@
         <v>683</v>
       </c>
       <c r="R110" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S110" s="49">
         <v>0</v>
       </c>
       <c r="T110" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U110" s="55">
         <v>0</v>
       </c>
       <c r="V110" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W110" s="55">
         <v>0</v>
@@ -27975,10 +27975,10 @@
         <v>1276</v>
       </c>
       <c r="AX110" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY110" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="111" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28034,19 +28034,19 @@
         <v>683</v>
       </c>
       <c r="R111" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S111" s="49">
         <v>0</v>
       </c>
       <c r="T111" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U111" s="55">
         <v>0</v>
       </c>
       <c r="V111" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W111" s="55">
         <v>0</v>
@@ -28130,10 +28130,10 @@
         <v>1276</v>
       </c>
       <c r="AX111" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY111" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="112" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28189,19 +28189,19 @@
         <v>683</v>
       </c>
       <c r="R112" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S112" s="49">
         <v>0</v>
       </c>
       <c r="T112" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U112" s="55">
         <v>0</v>
       </c>
       <c r="V112" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W112" s="55">
         <v>0</v>
@@ -28285,10 +28285,10 @@
         <v>1276</v>
       </c>
       <c r="AX112" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY112" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="113" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28344,19 +28344,19 @@
         <v>683</v>
       </c>
       <c r="R113" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S113" s="49">
         <v>50</v>
       </c>
       <c r="T113" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U113" s="55">
         <v>4</v>
       </c>
       <c r="V113" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W113" s="55">
         <v>10</v>
@@ -28440,10 +28440,10 @@
         <v>1276</v>
       </c>
       <c r="AX113" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY113" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="114" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28499,19 +28499,19 @@
         <v>422</v>
       </c>
       <c r="R114" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S114" s="49">
         <v>0</v>
       </c>
       <c r="T114" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U114" s="55">
         <v>0</v>
       </c>
       <c r="V114" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W114" s="55">
         <v>0</v>
@@ -28595,10 +28595,10 @@
         <v>1276</v>
       </c>
       <c r="AX114" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY114" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="115" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28654,19 +28654,19 @@
         <v>422</v>
       </c>
       <c r="R115" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S115" s="49">
         <v>0</v>
       </c>
       <c r="T115" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U115" s="55">
         <v>2</v>
       </c>
       <c r="V115" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W115" s="55">
         <v>4</v>
@@ -28750,10 +28750,10 @@
         <v>1276</v>
       </c>
       <c r="AX115" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY115" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="116" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28809,19 +28809,19 @@
         <v>683</v>
       </c>
       <c r="R116" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S116" s="49">
         <v>60</v>
       </c>
       <c r="T116" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U116" s="55">
         <v>6</v>
       </c>
       <c r="V116" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W116" s="55">
         <v>12</v>
@@ -28905,10 +28905,10 @@
         <v>1276</v>
       </c>
       <c r="AX116" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY116" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="117" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -28964,19 +28964,19 @@
         <v>683</v>
       </c>
       <c r="R117" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S117" s="49">
         <v>60</v>
       </c>
       <c r="T117" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U117" s="55">
         <v>5</v>
       </c>
       <c r="V117" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W117" s="55">
         <v>10</v>
@@ -29060,10 +29060,10 @@
         <v>1276</v>
       </c>
       <c r="AX117" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY117" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="118" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29119,19 +29119,19 @@
         <v>683</v>
       </c>
       <c r="R118" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S118" s="49">
         <v>80</v>
       </c>
       <c r="T118" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U118" s="55">
         <v>6</v>
       </c>
       <c r="V118" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W118" s="55">
         <v>12</v>
@@ -29215,10 +29215,10 @@
         <v>1276</v>
       </c>
       <c r="AX118" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY118" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="119" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29274,19 +29274,19 @@
         <v>683</v>
       </c>
       <c r="R119" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S119" s="49">
         <v>100</v>
       </c>
       <c r="T119" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U119" s="55">
         <v>8</v>
       </c>
       <c r="V119" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W119" s="55">
         <v>15</v>
@@ -29370,10 +29370,10 @@
         <v>1276</v>
       </c>
       <c r="AX119" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY119" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="120" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29429,19 +29429,19 @@
         <v>683</v>
       </c>
       <c r="R120" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S120" s="49">
         <v>50</v>
       </c>
       <c r="T120" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U120" s="55">
         <v>4</v>
       </c>
       <c r="V120" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W120" s="55">
         <v>10</v>
@@ -29525,10 +29525,10 @@
         <v>1276</v>
       </c>
       <c r="AX120" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY120" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="121" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29584,19 +29584,19 @@
         <v>684</v>
       </c>
       <c r="R121" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S121" s="49">
         <v>0</v>
       </c>
       <c r="T121" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U121" s="55">
         <v>3</v>
       </c>
       <c r="V121" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W121" s="55">
         <v>6</v>
@@ -29680,10 +29680,10 @@
         <v>1276</v>
       </c>
       <c r="AX121" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY121" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="122" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29739,19 +29739,19 @@
         <v>683</v>
       </c>
       <c r="R122" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S122" s="49">
         <v>60</v>
       </c>
       <c r="T122" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U122" s="55">
         <v>5</v>
       </c>
       <c r="V122" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W122" s="55">
         <v>10</v>
@@ -29835,10 +29835,10 @@
         <v>1276</v>
       </c>
       <c r="AX122" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY122" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="123" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -29894,19 +29894,19 @@
         <v>683</v>
       </c>
       <c r="R123" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S123" s="49">
         <v>100</v>
       </c>
       <c r="T123" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U123" s="55">
         <v>6</v>
       </c>
       <c r="V123" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W123" s="55">
         <v>12</v>
@@ -29990,10 +29990,10 @@
         <v>1276</v>
       </c>
       <c r="AX123" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY123" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="124" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30049,19 +30049,19 @@
         <v>683</v>
       </c>
       <c r="R124" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S124" s="49">
         <v>30</v>
       </c>
       <c r="T124" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U124" s="55">
         <v>4</v>
       </c>
       <c r="V124" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W124" s="55">
         <v>8</v>
@@ -30145,10 +30145,10 @@
         <v>1276</v>
       </c>
       <c r="AX124" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY124" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="125" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30204,19 +30204,19 @@
         <v>683</v>
       </c>
       <c r="R125" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S125" s="49">
         <v>30</v>
       </c>
       <c r="T125" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U125" s="55">
         <v>3</v>
       </c>
       <c r="V125" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W125" s="55">
         <v>6</v>
@@ -30300,10 +30300,10 @@
         <v>1276</v>
       </c>
       <c r="AX125" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY125" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="126" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30359,19 +30359,19 @@
         <v>1247</v>
       </c>
       <c r="R126" s="76" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S126" s="49">
         <v>10</v>
       </c>
       <c r="T126" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U126" s="55">
         <v>0</v>
       </c>
       <c r="V126" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W126" s="55">
         <v>0</v>
@@ -30455,10 +30455,10 @@
         <v>1276</v>
       </c>
       <c r="AX126" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY126" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="127" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30514,19 +30514,19 @@
         <v>1248</v>
       </c>
       <c r="R127" s="76" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S127" s="49">
         <v>30</v>
       </c>
       <c r="T127" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U127" s="55">
         <v>0</v>
       </c>
       <c r="V127" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W127" s="55">
         <v>0</v>
@@ -30610,10 +30610,10 @@
         <v>1276</v>
       </c>
       <c r="AX127" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY127" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="128" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30669,19 +30669,19 @@
         <v>1247</v>
       </c>
       <c r="R128" s="76" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S128" s="49">
         <v>10</v>
       </c>
       <c r="T128" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U128" s="55">
         <v>0</v>
       </c>
       <c r="V128" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W128" s="55">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>187</v>
       </c>
       <c r="AM128" s="44" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="AN128" s="77" t="s">
         <v>588</v>
@@ -30765,10 +30765,10 @@
         <v>1276</v>
       </c>
       <c r="AX128" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY128" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="129" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30824,19 +30824,19 @@
         <v>1247</v>
       </c>
       <c r="R129" s="76" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S129" s="49">
         <v>5</v>
       </c>
       <c r="T129" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U129" s="55">
         <v>0</v>
       </c>
       <c r="V129" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W129" s="55">
         <v>0</v>
@@ -30887,7 +30887,7 @@
         <v>187</v>
       </c>
       <c r="AM129" s="44" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="AN129" s="77" t="s">
         <v>588</v>
@@ -30920,10 +30920,10 @@
         <v>1276</v>
       </c>
       <c r="AX129" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY129" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="130" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -30979,19 +30979,19 @@
         <v>423</v>
       </c>
       <c r="R130" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S130" s="49">
         <v>0</v>
       </c>
       <c r="T130" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U130" s="55">
         <v>3</v>
       </c>
       <c r="V130" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W130" s="55">
         <v>6</v>
@@ -31075,10 +31075,10 @@
         <v>1276</v>
       </c>
       <c r="AX130" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY130" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="131" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31134,19 +31134,19 @@
         <v>423</v>
       </c>
       <c r="R131" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S131" s="49">
         <v>0</v>
       </c>
       <c r="T131" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U131" s="55">
         <v>3</v>
       </c>
       <c r="V131" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W131" s="55">
         <v>6</v>
@@ -31230,10 +31230,10 @@
         <v>1276</v>
       </c>
       <c r="AX131" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY131" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="132" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31289,19 +31289,19 @@
         <v>423</v>
       </c>
       <c r="R132" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S132" s="49">
         <v>0</v>
       </c>
       <c r="T132" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U132" s="55">
         <v>3</v>
       </c>
       <c r="V132" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W132" s="55">
         <v>6</v>
@@ -31385,10 +31385,10 @@
         <v>1276</v>
       </c>
       <c r="AX132" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY132" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="133" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31444,19 +31444,19 @@
         <v>423</v>
       </c>
       <c r="R133" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S133" s="49">
         <v>0</v>
       </c>
       <c r="T133" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U133" s="55">
         <v>3</v>
       </c>
       <c r="V133" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W133" s="55">
         <v>6</v>
@@ -31540,10 +31540,10 @@
         <v>1276</v>
       </c>
       <c r="AX133" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY133" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="134" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31599,19 +31599,19 @@
         <v>423</v>
       </c>
       <c r="R134" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S134" s="49">
         <v>0</v>
       </c>
       <c r="T134" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U134" s="55">
         <v>3</v>
       </c>
       <c r="V134" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W134" s="55">
         <v>6</v>
@@ -31695,10 +31695,10 @@
         <v>1276</v>
       </c>
       <c r="AX134" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY134" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="135" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31754,19 +31754,19 @@
         <v>582</v>
       </c>
       <c r="R135" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S135" s="49">
         <v>0</v>
       </c>
       <c r="T135" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U135" s="55">
         <v>6</v>
       </c>
       <c r="V135" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W135" s="55">
         <v>12</v>
@@ -31850,10 +31850,10 @@
         <v>1276</v>
       </c>
       <c r="AX135" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY135" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="136" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -31909,19 +31909,19 @@
         <v>683</v>
       </c>
       <c r="R136" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S136" s="49">
         <v>40</v>
       </c>
       <c r="T136" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U136" s="55">
         <v>4</v>
       </c>
       <c r="V136" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W136" s="55">
         <v>8</v>
@@ -32005,10 +32005,10 @@
         <v>1276</v>
       </c>
       <c r="AX136" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY136" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="137" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32064,19 +32064,19 @@
         <v>582</v>
       </c>
       <c r="R137" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S137" s="49">
         <v>0</v>
       </c>
       <c r="T137" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U137" s="55">
         <v>4</v>
       </c>
       <c r="V137" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W137" s="55">
         <v>8</v>
@@ -32160,10 +32160,10 @@
         <v>1276</v>
       </c>
       <c r="AX137" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY137" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="138" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32219,19 +32219,19 @@
         <v>683</v>
       </c>
       <c r="R138" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S138" s="49">
         <v>50</v>
       </c>
       <c r="T138" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U138" s="55">
         <v>5</v>
       </c>
       <c r="V138" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W138" s="55">
         <v>10</v>
@@ -32315,10 +32315,10 @@
         <v>1276</v>
       </c>
       <c r="AX138" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY138" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="139" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32374,19 +32374,19 @@
         <v>683</v>
       </c>
       <c r="R139" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S139" s="49">
         <v>50</v>
       </c>
       <c r="T139" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U139" s="55">
         <v>5</v>
       </c>
       <c r="V139" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W139" s="55">
         <v>10</v>
@@ -32470,10 +32470,10 @@
         <v>1276</v>
       </c>
       <c r="AX139" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY139" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="140" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32529,19 +32529,19 @@
         <v>992</v>
       </c>
       <c r="R140" s="76" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S140" s="49">
         <v>0.5</v>
       </c>
       <c r="T140" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U140" s="55">
         <v>1</v>
       </c>
       <c r="V140" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W140" s="55">
         <v>3</v>
@@ -32592,7 +32592,7 @@
         <v>187</v>
       </c>
       <c r="AM140" s="44" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="AN140" s="77" t="s">
         <v>588</v>
@@ -32625,10 +32625,10 @@
         <v>1276</v>
       </c>
       <c r="AX140" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY140" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="141" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32684,19 +32684,19 @@
         <v>683</v>
       </c>
       <c r="R141" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S141" s="49">
         <v>0</v>
       </c>
       <c r="T141" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U141" s="55">
         <v>3</v>
       </c>
       <c r="V141" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W141" s="55">
         <v>6</v>
@@ -32780,10 +32780,10 @@
         <v>1276</v>
       </c>
       <c r="AX141" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY141" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="142" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32839,19 +32839,19 @@
         <v>683</v>
       </c>
       <c r="R142" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S142" s="49">
         <v>0</v>
       </c>
       <c r="T142" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U142" s="55">
         <v>5</v>
       </c>
       <c r="V142" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W142" s="55">
         <v>10</v>
@@ -32935,10 +32935,10 @@
         <v>1276</v>
       </c>
       <c r="AX142" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY142" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="143" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -32994,19 +32994,19 @@
         <v>683</v>
       </c>
       <c r="R143" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S143" s="49">
         <v>0</v>
       </c>
       <c r="T143" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U143" s="55">
         <v>5</v>
       </c>
       <c r="V143" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W143" s="55">
         <v>10</v>
@@ -33090,10 +33090,10 @@
         <v>1276</v>
       </c>
       <c r="AX143" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY143" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="144" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33149,19 +33149,19 @@
         <v>683</v>
       </c>
       <c r="R144" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S144" s="49">
         <v>0</v>
       </c>
       <c r="T144" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U144" s="55">
         <v>0</v>
       </c>
       <c r="V144" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W144" s="55">
         <v>0</v>
@@ -33245,10 +33245,10 @@
         <v>1276</v>
       </c>
       <c r="AX144" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY144" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="145" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33304,19 +33304,19 @@
         <v>683</v>
       </c>
       <c r="R145" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S145" s="49">
         <v>0</v>
       </c>
       <c r="T145" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U145" s="55">
         <v>3</v>
       </c>
       <c r="V145" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W145" s="55">
         <v>6</v>
@@ -33400,10 +33400,10 @@
         <v>1276</v>
       </c>
       <c r="AX145" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY145" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="146" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33459,19 +33459,19 @@
         <v>683</v>
       </c>
       <c r="R146" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S146" s="49">
         <v>60</v>
       </c>
       <c r="T146" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U146" s="55">
         <v>5</v>
       </c>
       <c r="V146" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W146" s="55">
         <v>10</v>
@@ -33555,10 +33555,10 @@
         <v>1276</v>
       </c>
       <c r="AX146" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY146" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="147" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33614,19 +33614,19 @@
         <v>683</v>
       </c>
       <c r="R147" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S147" s="49">
         <v>50</v>
       </c>
       <c r="T147" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U147" s="55">
         <v>5</v>
       </c>
       <c r="V147" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W147" s="55">
         <v>10</v>
@@ -33710,10 +33710,10 @@
         <v>1276</v>
       </c>
       <c r="AX147" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY147" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="148" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33769,19 +33769,19 @@
         <v>683</v>
       </c>
       <c r="R148" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S148" s="49">
         <v>50</v>
       </c>
       <c r="T148" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U148" s="55">
         <v>5</v>
       </c>
       <c r="V148" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W148" s="55">
         <v>10</v>
@@ -33865,10 +33865,10 @@
         <v>1276</v>
       </c>
       <c r="AX148" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY148" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="149" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -33924,19 +33924,19 @@
         <v>422</v>
       </c>
       <c r="R149" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S149" s="49">
         <v>0</v>
       </c>
       <c r="T149" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U149" s="55">
         <v>0</v>
       </c>
       <c r="V149" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W149" s="55">
         <v>0</v>
@@ -34020,10 +34020,10 @@
         <v>1276</v>
       </c>
       <c r="AX149" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY149" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="150" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34079,19 +34079,19 @@
         <v>422</v>
       </c>
       <c r="R150" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S150" s="49">
         <v>0</v>
       </c>
       <c r="T150" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U150" s="55">
         <v>2</v>
       </c>
       <c r="V150" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W150" s="55">
         <v>4</v>
@@ -34175,10 +34175,10 @@
         <v>1276</v>
       </c>
       <c r="AX150" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY150" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="151" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34234,19 +34234,19 @@
         <v>683</v>
       </c>
       <c r="R151" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S151" s="49">
         <v>50</v>
       </c>
       <c r="T151" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U151" s="55">
         <v>5</v>
       </c>
       <c r="V151" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W151" s="55">
         <v>10</v>
@@ -34330,10 +34330,10 @@
         <v>1276</v>
       </c>
       <c r="AX151" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY151" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="152" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34389,19 +34389,19 @@
         <v>683</v>
       </c>
       <c r="R152" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S152" s="49">
         <v>60</v>
       </c>
       <c r="T152" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U152" s="55">
         <v>5</v>
       </c>
       <c r="V152" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W152" s="55">
         <v>10</v>
@@ -34485,10 +34485,10 @@
         <v>1276</v>
       </c>
       <c r="AX152" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY152" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="153" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34544,19 +34544,19 @@
         <v>683</v>
       </c>
       <c r="R153" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S153" s="49">
         <v>50</v>
       </c>
       <c r="T153" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U153" s="55">
         <v>5</v>
       </c>
       <c r="V153" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W153" s="55">
         <v>10</v>
@@ -34640,10 +34640,10 @@
         <v>1276</v>
       </c>
       <c r="AX153" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY153" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="154" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34699,19 +34699,19 @@
         <v>582</v>
       </c>
       <c r="R154" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S154" s="49">
         <v>30</v>
       </c>
       <c r="T154" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U154" s="55">
         <v>4</v>
       </c>
       <c r="V154" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W154" s="55">
         <v>8</v>
@@ -34795,10 +34795,10 @@
         <v>1276</v>
       </c>
       <c r="AX154" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY154" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="155" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -34854,19 +34854,19 @@
         <v>683</v>
       </c>
       <c r="R155" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S155" s="49">
         <v>40</v>
       </c>
       <c r="T155" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U155" s="55">
         <v>4</v>
       </c>
       <c r="V155" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W155" s="55">
         <v>8</v>
@@ -34950,10 +34950,10 @@
         <v>1276</v>
       </c>
       <c r="AX155" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY155" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="156" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35009,19 +35009,19 @@
         <v>683</v>
       </c>
       <c r="R156" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S156" s="49">
         <v>40</v>
       </c>
       <c r="T156" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U156" s="55">
         <v>4</v>
       </c>
       <c r="V156" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W156" s="55">
         <v>8</v>
@@ -35105,10 +35105,10 @@
         <v>1276</v>
       </c>
       <c r="AX156" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY156" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="157" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35164,19 +35164,19 @@
         <v>683</v>
       </c>
       <c r="R157" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S157" s="49">
         <v>100</v>
       </c>
       <c r="T157" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U157" s="55">
         <v>10</v>
       </c>
       <c r="V157" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W157" s="55">
         <v>20</v>
@@ -35260,10 +35260,10 @@
         <v>1276</v>
       </c>
       <c r="AX157" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY157" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="158" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35319,19 +35319,19 @@
         <v>683</v>
       </c>
       <c r="R158" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S158" s="49">
         <v>60</v>
       </c>
       <c r="T158" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U158" s="55">
         <v>5</v>
       </c>
       <c r="V158" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W158" s="55">
         <v>10</v>
@@ -35415,10 +35415,10 @@
         <v>1276</v>
       </c>
       <c r="AX158" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY158" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="159" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35474,19 +35474,19 @@
         <v>683</v>
       </c>
       <c r="R159" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S159" s="49">
         <v>40</v>
       </c>
       <c r="T159" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U159" s="55">
         <v>4</v>
       </c>
       <c r="V159" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W159" s="55">
         <v>8</v>
@@ -35570,10 +35570,10 @@
         <v>1276</v>
       </c>
       <c r="AX159" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY159" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="160" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35629,19 +35629,19 @@
         <v>683</v>
       </c>
       <c r="R160" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S160" s="49">
         <v>60</v>
       </c>
       <c r="T160" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U160" s="55">
         <v>5</v>
       </c>
       <c r="V160" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W160" s="55">
         <v>10</v>
@@ -35725,10 +35725,10 @@
         <v>1276</v>
       </c>
       <c r="AX160" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY160" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="161" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35784,19 +35784,19 @@
         <v>582</v>
       </c>
       <c r="R161" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S161" s="49">
         <v>40</v>
       </c>
       <c r="T161" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U161" s="55">
         <v>4</v>
       </c>
       <c r="V161" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W161" s="55">
         <v>8</v>
@@ -35880,10 +35880,10 @@
         <v>1276</v>
       </c>
       <c r="AX161" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY161" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="162" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -35939,19 +35939,19 @@
         <v>684</v>
       </c>
       <c r="R162" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S162" s="49">
         <v>0</v>
       </c>
       <c r="T162" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U162" s="55">
         <v>0</v>
       </c>
       <c r="V162" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W162" s="55">
         <v>0</v>
@@ -36035,10 +36035,10 @@
         <v>1276</v>
       </c>
       <c r="AX162" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY162" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="163" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36094,19 +36094,19 @@
         <v>683</v>
       </c>
       <c r="R163" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S163" s="49">
         <v>30</v>
       </c>
       <c r="T163" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U163" s="55">
         <v>4</v>
       </c>
       <c r="V163" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W163" s="55">
         <v>8</v>
@@ -36190,10 +36190,10 @@
         <v>1276</v>
       </c>
       <c r="AX163" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY163" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="164" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36249,19 +36249,19 @@
         <v>683</v>
       </c>
       <c r="R164" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S164" s="49">
         <v>30</v>
       </c>
       <c r="T164" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U164" s="55">
         <v>3</v>
       </c>
       <c r="V164" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W164" s="55">
         <v>6</v>
@@ -36345,10 +36345,10 @@
         <v>1276</v>
       </c>
       <c r="AX164" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY164" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="165" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36404,19 +36404,19 @@
         <v>422</v>
       </c>
       <c r="R165" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S165" s="49">
         <v>0</v>
       </c>
       <c r="T165" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U165" s="55">
         <v>2</v>
       </c>
       <c r="V165" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W165" s="55">
         <v>4</v>
@@ -36500,10 +36500,10 @@
         <v>1276</v>
       </c>
       <c r="AX165" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY165" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="166" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36559,19 +36559,19 @@
         <v>683</v>
       </c>
       <c r="R166" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S166" s="49">
         <v>60</v>
       </c>
       <c r="T166" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U166" s="55">
         <v>5</v>
       </c>
       <c r="V166" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W166" s="55">
         <v>10</v>
@@ -36655,10 +36655,10 @@
         <v>1276</v>
       </c>
       <c r="AX166" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY166" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="167" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36714,19 +36714,19 @@
         <v>683</v>
       </c>
       <c r="R167" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S167" s="49">
         <v>50</v>
       </c>
       <c r="T167" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U167" s="55">
         <v>4</v>
       </c>
       <c r="V167" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W167" s="55">
         <v>12</v>
@@ -36810,10 +36810,10 @@
         <v>1276</v>
       </c>
       <c r="AX167" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY167" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="168" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -36869,19 +36869,19 @@
         <v>683</v>
       </c>
       <c r="R168" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S168" s="49">
         <v>40</v>
       </c>
       <c r="T168" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U168" s="55">
         <v>3</v>
       </c>
       <c r="V168" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W168" s="55">
         <v>10</v>
@@ -36965,10 +36965,10 @@
         <v>1276</v>
       </c>
       <c r="AX168" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY168" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="169" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37024,19 +37024,19 @@
         <v>683</v>
       </c>
       <c r="R169" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S169" s="49">
         <v>0</v>
       </c>
       <c r="T169" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U169" s="55">
         <v>0</v>
       </c>
       <c r="V169" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W169" s="55">
         <v>0</v>
@@ -37120,10 +37120,10 @@
         <v>1276</v>
       </c>
       <c r="AX169" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY169" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="170" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37179,19 +37179,19 @@
         <v>684</v>
       </c>
       <c r="R170" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S170" s="49">
         <v>0</v>
       </c>
       <c r="T170" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U170" s="55">
         <v>3</v>
       </c>
       <c r="V170" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W170" s="55">
         <v>6</v>
@@ -37275,10 +37275,10 @@
         <v>1276</v>
       </c>
       <c r="AX170" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY170" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="171" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37334,19 +37334,19 @@
         <v>684</v>
       </c>
       <c r="R171" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S171" s="49">
         <v>30</v>
       </c>
       <c r="T171" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U171" s="55">
         <v>3</v>
       </c>
       <c r="V171" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W171" s="55">
         <v>6</v>
@@ -37397,7 +37397,7 @@
         <v>187</v>
       </c>
       <c r="AM171" s="44" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="AN171" s="47" t="s">
         <v>588</v>
@@ -37430,10 +37430,10 @@
         <v>1276</v>
       </c>
       <c r="AX171" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY171" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="172" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37489,19 +37489,19 @@
         <v>683</v>
       </c>
       <c r="R172" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S172" s="49">
         <v>30</v>
       </c>
       <c r="T172" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U172" s="55">
         <v>3</v>
       </c>
       <c r="V172" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W172" s="55">
         <v>6</v>
@@ -37585,10 +37585,10 @@
         <v>1276</v>
       </c>
       <c r="AX172" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY172" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="173" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37644,19 +37644,19 @@
         <v>683</v>
       </c>
       <c r="R173" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S173" s="49">
         <v>60</v>
       </c>
       <c r="T173" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U173" s="55">
         <v>6</v>
       </c>
       <c r="V173" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W173" s="55">
         <v>12</v>
@@ -37740,10 +37740,10 @@
         <v>1276</v>
       </c>
       <c r="AX173" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY173" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="174" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37799,19 +37799,19 @@
         <v>683</v>
       </c>
       <c r="R174" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S174" s="49">
         <v>60</v>
       </c>
       <c r="T174" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U174" s="55">
         <v>6</v>
       </c>
       <c r="V174" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W174" s="55">
         <v>12</v>
@@ -37895,10 +37895,10 @@
         <v>1276</v>
       </c>
       <c r="AX174" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY174" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="175" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -37954,19 +37954,19 @@
         <v>683</v>
       </c>
       <c r="R175" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S175" s="49">
         <v>60</v>
       </c>
       <c r="T175" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U175" s="55">
         <v>6</v>
       </c>
       <c r="V175" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W175" s="55">
         <v>12</v>
@@ -38050,10 +38050,10 @@
         <v>1276</v>
       </c>
       <c r="AX175" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY175" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="176" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38109,19 +38109,19 @@
         <v>683</v>
       </c>
       <c r="R176" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S176" s="49">
         <v>60</v>
       </c>
       <c r="T176" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U176" s="55">
         <v>0</v>
       </c>
       <c r="V176" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W176" s="55">
         <v>0</v>
@@ -38205,10 +38205,10 @@
         <v>1276</v>
       </c>
       <c r="AX176" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY176" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="177" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38264,19 +38264,19 @@
         <v>683</v>
       </c>
       <c r="R177" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S177" s="49">
         <v>60</v>
       </c>
       <c r="T177" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U177" s="55">
         <v>0</v>
       </c>
       <c r="V177" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W177" s="55">
         <v>0</v>
@@ -38360,10 +38360,10 @@
         <v>1276</v>
       </c>
       <c r="AX177" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY177" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="178" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38419,19 +38419,19 @@
         <v>683</v>
       </c>
       <c r="R178" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S178" s="49">
         <v>60</v>
       </c>
       <c r="T178" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U178" s="55">
         <v>0</v>
       </c>
       <c r="V178" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W178" s="55">
         <v>0</v>
@@ -38515,10 +38515,10 @@
         <v>1276</v>
       </c>
       <c r="AX178" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY178" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="179" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38574,19 +38574,19 @@
         <v>683</v>
       </c>
       <c r="R179" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S179" s="49">
         <v>60</v>
       </c>
       <c r="T179" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U179" s="55">
         <v>6</v>
       </c>
       <c r="V179" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W179" s="55">
         <v>12</v>
@@ -38637,7 +38637,7 @@
         <v>187</v>
       </c>
       <c r="AM179" s="44" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="AN179" s="47" t="s">
         <v>588</v>
@@ -38670,10 +38670,10 @@
         <v>1276</v>
       </c>
       <c r="AX179" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY179" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="180" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38729,19 +38729,19 @@
         <v>683</v>
       </c>
       <c r="R180" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S180" s="49">
         <v>50</v>
       </c>
       <c r="T180" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U180" s="55">
         <v>6</v>
       </c>
       <c r="V180" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W180" s="55">
         <v>12</v>
@@ -38825,10 +38825,10 @@
         <v>1276</v>
       </c>
       <c r="AX180" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY180" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="181" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -38884,19 +38884,19 @@
         <v>683</v>
       </c>
       <c r="R181" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S181" s="49">
         <v>50</v>
       </c>
       <c r="T181" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U181" s="55">
         <v>5</v>
       </c>
       <c r="V181" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W181" s="55">
         <v>10</v>
@@ -38980,10 +38980,10 @@
         <v>1276</v>
       </c>
       <c r="AX181" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY181" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="182" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39039,19 +39039,19 @@
         <v>683</v>
       </c>
       <c r="R182" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S182" s="49">
         <v>60</v>
       </c>
       <c r="T182" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U182" s="55">
         <v>6</v>
       </c>
       <c r="V182" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W182" s="55">
         <v>12</v>
@@ -39135,10 +39135,10 @@
         <v>1276</v>
       </c>
       <c r="AX182" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY182" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="183" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39194,19 +39194,19 @@
         <v>683</v>
       </c>
       <c r="R183" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S183" s="49">
         <v>30</v>
       </c>
       <c r="T183" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U183" s="55">
         <v>3</v>
       </c>
       <c r="V183" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W183" s="55">
         <v>6</v>
@@ -39290,10 +39290,10 @@
         <v>1276</v>
       </c>
       <c r="AX183" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY183" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="184" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39349,19 +39349,19 @@
         <v>683</v>
       </c>
       <c r="R184" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S184" s="49">
         <v>100</v>
       </c>
       <c r="T184" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U184" s="55">
         <v>8</v>
       </c>
       <c r="V184" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W184" s="55">
         <v>15</v>
@@ -39445,10 +39445,10 @@
         <v>1276</v>
       </c>
       <c r="AX184" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY184" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="185" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39504,19 +39504,19 @@
         <v>683</v>
       </c>
       <c r="R185" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S185" s="49">
         <v>50</v>
       </c>
       <c r="T185" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U185" s="55">
         <v>5</v>
       </c>
       <c r="V185" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W185" s="55">
         <v>10</v>
@@ -39600,10 +39600,10 @@
         <v>1276</v>
       </c>
       <c r="AX185" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY185" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="186" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39659,19 +39659,19 @@
         <v>683</v>
       </c>
       <c r="R186" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S186" s="49">
         <v>60</v>
       </c>
       <c r="T186" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U186" s="55">
         <v>5</v>
       </c>
       <c r="V186" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W186" s="55">
         <v>10</v>
@@ -39755,10 +39755,10 @@
         <v>1276</v>
       </c>
       <c r="AX186" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY186" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="187" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39814,19 +39814,19 @@
         <v>683</v>
       </c>
       <c r="R187" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S187" s="49">
         <v>50</v>
       </c>
       <c r="T187" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U187" s="55">
         <v>5</v>
       </c>
       <c r="V187" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W187" s="55">
         <v>10</v>
@@ -39910,10 +39910,10 @@
         <v>1276</v>
       </c>
       <c r="AX187" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY187" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="188" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -39969,19 +39969,19 @@
         <v>683</v>
       </c>
       <c r="R188" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S188" s="49">
         <v>50</v>
       </c>
       <c r="T188" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U188" s="55">
         <v>4</v>
       </c>
       <c r="V188" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W188" s="55">
         <v>8</v>
@@ -40065,10 +40065,10 @@
         <v>1276</v>
       </c>
       <c r="AX188" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY188" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="189" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40124,19 +40124,19 @@
         <v>683</v>
       </c>
       <c r="R189" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S189" s="49">
         <v>50</v>
       </c>
       <c r="T189" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U189" s="55">
         <v>4</v>
       </c>
       <c r="V189" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W189" s="55">
         <v>8</v>
@@ -40220,10 +40220,10 @@
         <v>1276</v>
       </c>
       <c r="AX189" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY189" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="190" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40279,19 +40279,19 @@
         <v>684</v>
       </c>
       <c r="R190" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S190" s="49">
         <v>0</v>
       </c>
       <c r="T190" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U190" s="55">
         <v>2</v>
       </c>
       <c r="V190" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W190" s="55">
         <v>4</v>
@@ -40375,10 +40375,10 @@
         <v>1276</v>
       </c>
       <c r="AX190" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY190" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="191" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40434,19 +40434,19 @@
         <v>683</v>
       </c>
       <c r="R191" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S191" s="49">
         <v>50</v>
       </c>
       <c r="T191" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U191" s="55">
         <v>4</v>
       </c>
       <c r="V191" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W191" s="55">
         <v>8</v>
@@ -40530,10 +40530,10 @@
         <v>1276</v>
       </c>
       <c r="AX191" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY191" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="192" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40589,19 +40589,19 @@
         <v>683</v>
       </c>
       <c r="R192" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S192" s="49">
         <v>30</v>
       </c>
       <c r="T192" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U192" s="55">
         <v>3</v>
       </c>
       <c r="V192" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W192" s="55">
         <v>6</v>
@@ -40685,10 +40685,10 @@
         <v>1276</v>
       </c>
       <c r="AX192" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY192" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="193" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40744,19 +40744,19 @@
         <v>683</v>
       </c>
       <c r="R193" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S193" s="49">
         <v>60</v>
       </c>
       <c r="T193" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U193" s="55">
         <v>5</v>
       </c>
       <c r="V193" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W193" s="55">
         <v>10</v>
@@ -40840,10 +40840,10 @@
         <v>1276</v>
       </c>
       <c r="AX193" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY193" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="194" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -40899,19 +40899,19 @@
         <v>683</v>
       </c>
       <c r="R194" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S194" s="49">
         <v>60</v>
       </c>
       <c r="T194" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U194" s="55">
         <v>5</v>
       </c>
       <c r="V194" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W194" s="55">
         <v>10</v>
@@ -40995,10 +40995,10 @@
         <v>1276</v>
       </c>
       <c r="AX194" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY194" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="195" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41054,19 +41054,19 @@
         <v>683</v>
       </c>
       <c r="R195" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S195" s="49">
         <v>50</v>
       </c>
       <c r="T195" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U195" s="55">
         <v>5</v>
       </c>
       <c r="V195" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W195" s="55">
         <v>10</v>
@@ -41150,10 +41150,10 @@
         <v>1276</v>
       </c>
       <c r="AX195" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY195" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="196" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41209,19 +41209,19 @@
         <v>683</v>
       </c>
       <c r="R196" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S196" s="49">
         <v>50</v>
       </c>
       <c r="T196" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U196" s="55">
         <v>5</v>
       </c>
       <c r="V196" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W196" s="55">
         <v>10</v>
@@ -41305,10 +41305,10 @@
         <v>1276</v>
       </c>
       <c r="AX196" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY196" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="197" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41364,19 +41364,19 @@
         <v>683</v>
       </c>
       <c r="R197" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S197" s="49">
         <v>50</v>
       </c>
       <c r="T197" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U197" s="55">
         <v>5</v>
       </c>
       <c r="V197" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W197" s="55">
         <v>10</v>
@@ -41460,10 +41460,10 @@
         <v>1276</v>
       </c>
       <c r="AX197" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY197" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="198" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41519,19 +41519,19 @@
         <v>683</v>
       </c>
       <c r="R198" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S198" s="49">
         <v>50</v>
       </c>
       <c r="T198" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U198" s="55">
         <v>5</v>
       </c>
       <c r="V198" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W198" s="55">
         <v>10</v>
@@ -41615,10 +41615,10 @@
         <v>1276</v>
       </c>
       <c r="AX198" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY198" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="199" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41674,19 +41674,19 @@
         <v>683</v>
       </c>
       <c r="R199" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S199" s="49">
         <v>50</v>
       </c>
       <c r="T199" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U199" s="55">
         <v>5</v>
       </c>
       <c r="V199" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W199" s="55">
         <v>10</v>
@@ -41770,10 +41770,10 @@
         <v>1276</v>
       </c>
       <c r="AX199" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY199" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="200" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41829,19 +41829,19 @@
         <v>683</v>
       </c>
       <c r="R200" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S200" s="49">
         <v>100</v>
       </c>
       <c r="T200" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U200" s="55">
         <v>6</v>
       </c>
       <c r="V200" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W200" s="55">
         <v>12</v>
@@ -41925,10 +41925,10 @@
         <v>1276</v>
       </c>
       <c r="AX200" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY200" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="201" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -41984,19 +41984,19 @@
         <v>683</v>
       </c>
       <c r="R201" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S201" s="49">
         <v>50</v>
       </c>
       <c r="T201" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U201" s="55">
         <v>5</v>
       </c>
       <c r="V201" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W201" s="55">
         <v>10</v>
@@ -42080,10 +42080,10 @@
         <v>1276</v>
       </c>
       <c r="AX201" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY201" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="202" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42139,19 +42139,19 @@
         <v>683</v>
       </c>
       <c r="R202" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S202" s="49">
         <v>100</v>
       </c>
       <c r="T202" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U202" s="55">
         <v>8</v>
       </c>
       <c r="V202" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W202" s="55">
         <v>15</v>
@@ -42235,10 +42235,10 @@
         <v>1276</v>
       </c>
       <c r="AX202" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY202" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="203" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42294,19 +42294,19 @@
         <v>683</v>
       </c>
       <c r="R203" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S203" s="49">
         <v>200</v>
       </c>
       <c r="T203" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U203" s="55">
         <v>10</v>
       </c>
       <c r="V203" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W203" s="55">
         <v>20</v>
@@ -42390,10 +42390,10 @@
         <v>1276</v>
       </c>
       <c r="AX203" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY203" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="204" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42449,19 +42449,19 @@
         <v>683</v>
       </c>
       <c r="R204" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S204" s="49">
         <v>80</v>
       </c>
       <c r="T204" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U204" s="55">
         <v>0</v>
       </c>
       <c r="V204" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W204" s="55">
         <v>0</v>
@@ -42545,10 +42545,10 @@
         <v>1276</v>
       </c>
       <c r="AX204" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY204" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="205" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42604,19 +42604,19 @@
         <v>683</v>
       </c>
       <c r="R205" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S205" s="49">
         <v>50</v>
       </c>
       <c r="T205" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U205" s="55">
         <v>5</v>
       </c>
       <c r="V205" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W205" s="55">
         <v>10</v>
@@ -42700,10 +42700,10 @@
         <v>1276</v>
       </c>
       <c r="AX205" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY205" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="206" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42759,19 +42759,19 @@
         <v>683</v>
       </c>
       <c r="R206" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S206" s="49">
         <v>50</v>
       </c>
       <c r="T206" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U206" s="55">
         <v>5</v>
       </c>
       <c r="V206" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W206" s="55">
         <v>10</v>
@@ -42855,10 +42855,10 @@
         <v>1276</v>
       </c>
       <c r="AX206" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY206" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="207" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -42914,19 +42914,19 @@
         <v>683</v>
       </c>
       <c r="R207" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S207" s="49">
         <v>30</v>
       </c>
       <c r="T207" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U207" s="55">
         <v>3</v>
       </c>
       <c r="V207" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W207" s="55">
         <v>6</v>
@@ -43010,10 +43010,10 @@
         <v>1276</v>
       </c>
       <c r="AX207" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY207" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="208" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43069,19 +43069,19 @@
         <v>422</v>
       </c>
       <c r="R208" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S208" s="49">
         <v>0</v>
       </c>
       <c r="T208" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U208" s="55">
         <v>2</v>
       </c>
       <c r="V208" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W208" s="55">
         <v>4</v>
@@ -43165,10 +43165,10 @@
         <v>1276</v>
       </c>
       <c r="AX208" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY208" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="209" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43224,19 +43224,19 @@
         <v>423</v>
       </c>
       <c r="R209" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S209" s="49">
         <v>0</v>
       </c>
       <c r="T209" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U209" s="55">
         <v>0</v>
       </c>
       <c r="V209" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W209" s="55">
         <v>0</v>
@@ -43320,10 +43320,10 @@
         <v>1276</v>
       </c>
       <c r="AX209" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY209" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="210" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43379,19 +43379,19 @@
         <v>683</v>
       </c>
       <c r="R210" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S210" s="49">
         <v>100</v>
       </c>
       <c r="T210" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U210" s="55">
         <v>6</v>
       </c>
       <c r="V210" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W210" s="55">
         <v>12</v>
@@ -43475,10 +43475,10 @@
         <v>1276</v>
       </c>
       <c r="AX210" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY210" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="211" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43534,19 +43534,19 @@
         <v>683</v>
       </c>
       <c r="R211" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S211" s="49">
         <v>40</v>
       </c>
       <c r="T211" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U211" s="55">
         <v>4</v>
       </c>
       <c r="V211" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W211" s="55">
         <v>8</v>
@@ -43630,10 +43630,10 @@
         <v>1276</v>
       </c>
       <c r="AX211" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY211" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="212" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43689,19 +43689,19 @@
         <v>683</v>
       </c>
       <c r="R212" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S212" s="49">
         <v>0</v>
       </c>
       <c r="T212" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U212" s="55">
         <v>3</v>
       </c>
       <c r="V212" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W212" s="55">
         <v>6</v>
@@ -43785,10 +43785,10 @@
         <v>1276</v>
       </c>
       <c r="AX212" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY212" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="213" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43844,19 +43844,19 @@
         <v>422</v>
       </c>
       <c r="R213" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S213" s="49">
         <v>20</v>
       </c>
       <c r="T213" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U213" s="55">
         <v>2</v>
       </c>
       <c r="V213" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W213" s="55">
         <v>4</v>
@@ -43940,10 +43940,10 @@
         <v>1276</v>
       </c>
       <c r="AX213" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY213" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="214" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -43999,19 +43999,19 @@
         <v>683</v>
       </c>
       <c r="R214" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S214" s="49">
         <v>40</v>
       </c>
       <c r="T214" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U214" s="55">
         <v>4</v>
       </c>
       <c r="V214" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W214" s="55">
         <v>8</v>
@@ -44095,10 +44095,10 @@
         <v>1276</v>
       </c>
       <c r="AX214" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY214" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="215" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44154,19 +44154,19 @@
         <v>422</v>
       </c>
       <c r="R215" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S215" s="49">
         <v>0</v>
       </c>
       <c r="T215" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U215" s="55">
         <v>2</v>
       </c>
       <c r="V215" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W215" s="55">
         <v>4</v>
@@ -44250,10 +44250,10 @@
         <v>1276</v>
       </c>
       <c r="AX215" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY215" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="216" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44309,19 +44309,19 @@
         <v>683</v>
       </c>
       <c r="R216" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S216" s="49">
         <v>40</v>
       </c>
       <c r="T216" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U216" s="55">
         <v>4</v>
       </c>
       <c r="V216" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W216" s="55">
         <v>8</v>
@@ -44405,10 +44405,10 @@
         <v>1276</v>
       </c>
       <c r="AX216" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY216" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="217" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44464,19 +44464,19 @@
         <v>683</v>
       </c>
       <c r="R217" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S217" s="49">
         <v>60</v>
       </c>
       <c r="T217" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U217" s="55">
         <v>5</v>
       </c>
       <c r="V217" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W217" s="55">
         <v>10</v>
@@ -44560,10 +44560,10 @@
         <v>1276</v>
       </c>
       <c r="AX217" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY217" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="218" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44619,19 +44619,19 @@
         <v>683</v>
       </c>
       <c r="R218" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S218" s="49">
         <v>50</v>
       </c>
       <c r="T218" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U218" s="55">
         <v>5</v>
       </c>
       <c r="V218" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W218" s="55">
         <v>10</v>
@@ -44715,10 +44715,10 @@
         <v>1276</v>
       </c>
       <c r="AX218" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY218" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="219" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44774,19 +44774,19 @@
         <v>683</v>
       </c>
       <c r="R219" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S219" s="49">
         <v>60</v>
       </c>
       <c r="T219" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U219" s="55">
         <v>6</v>
       </c>
       <c r="V219" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W219" s="55">
         <v>12</v>
@@ -44870,10 +44870,10 @@
         <v>1276</v>
       </c>
       <c r="AX219" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY219" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="220" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -44929,19 +44929,19 @@
         <v>582</v>
       </c>
       <c r="R220" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S220" s="49">
         <v>0</v>
       </c>
       <c r="T220" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U220" s="55">
         <v>4</v>
       </c>
       <c r="V220" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W220" s="55">
         <v>8</v>
@@ -45025,10 +45025,10 @@
         <v>1276</v>
       </c>
       <c r="AX220" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY220" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="221" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45084,19 +45084,19 @@
         <v>582</v>
       </c>
       <c r="R221" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S221" s="49">
         <v>0</v>
       </c>
       <c r="T221" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U221" s="55">
         <v>2</v>
       </c>
       <c r="V221" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W221" s="55">
         <v>4</v>
@@ -45180,10 +45180,10 @@
         <v>1276</v>
       </c>
       <c r="AX221" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY221" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="222" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45239,19 +45239,19 @@
         <v>582</v>
       </c>
       <c r="R222" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S222" s="49">
         <v>50</v>
       </c>
       <c r="T222" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U222" s="55">
         <v>5</v>
       </c>
       <c r="V222" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W222" s="55">
         <v>10</v>
@@ -45302,7 +45302,7 @@
         <v>187</v>
       </c>
       <c r="AM222" s="44" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AN222" s="47" t="s">
         <v>588</v>
@@ -45335,10 +45335,10 @@
         <v>1276</v>
       </c>
       <c r="AX222" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY222" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="223" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45394,19 +45394,19 @@
         <v>582</v>
       </c>
       <c r="R223" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S223" s="49">
         <v>0</v>
       </c>
       <c r="T223" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U223" s="55">
         <v>2</v>
       </c>
       <c r="V223" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W223" s="55">
         <v>4</v>
@@ -45490,10 +45490,10 @@
         <v>1276</v>
       </c>
       <c r="AX223" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY223" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="224" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45549,19 +45549,19 @@
         <v>582</v>
       </c>
       <c r="R224" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S224" s="49">
         <v>40</v>
       </c>
       <c r="T224" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U224" s="55">
         <v>4</v>
       </c>
       <c r="V224" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W224" s="55">
         <v>8</v>
@@ -45645,10 +45645,10 @@
         <v>1276</v>
       </c>
       <c r="AX224" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY224" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="225" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45704,19 +45704,19 @@
         <v>582</v>
       </c>
       <c r="R225" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S225" s="49">
         <v>40</v>
       </c>
       <c r="T225" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U225" s="55">
         <v>4</v>
       </c>
       <c r="V225" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W225" s="55">
         <v>8</v>
@@ -45800,10 +45800,10 @@
         <v>1276</v>
       </c>
       <c r="AX225" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY225" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="226" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -45811,7 +45811,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="69" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C226" s="32" t="s">
         <v>581</v>
@@ -45859,19 +45859,19 @@
         <v>582</v>
       </c>
       <c r="R226" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S226" s="49">
         <v>130</v>
       </c>
       <c r="T226" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U226" s="55">
         <v>3</v>
       </c>
       <c r="V226" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W226" s="55">
         <v>5</v>
@@ -45898,7 +45898,7 @@
         <v>180</v>
       </c>
       <c r="AE226" s="49" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="AF226" s="68" t="s">
         <v>181</v>
@@ -45916,19 +45916,19 @@
         <v>182</v>
       </c>
       <c r="AK226" s="44" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="AL226" s="68" t="s">
         <v>187</v>
       </c>
       <c r="AM226" s="45" t="s">
-        <v>1280</v>
+        <v>1329</v>
       </c>
       <c r="AN226" s="47" t="s">
         <v>588</v>
       </c>
       <c r="AO226" s="55" t="s">
-        <v>1284</v>
+        <v>1330</v>
       </c>
       <c r="AP226" s="47" t="s">
         <v>188</v>
@@ -45955,10 +45955,10 @@
         <v>1276</v>
       </c>
       <c r="AX226" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY226" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="227" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46014,19 +46014,19 @@
         <v>683</v>
       </c>
       <c r="R227" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S227" s="49">
         <v>30</v>
       </c>
       <c r="T227" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U227" s="55">
         <v>3</v>
       </c>
       <c r="V227" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W227" s="55">
         <v>6</v>
@@ -46110,10 +46110,10 @@
         <v>1276</v>
       </c>
       <c r="AX227" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY227" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="228" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46169,19 +46169,19 @@
         <v>683</v>
       </c>
       <c r="R228" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S228" s="49">
         <v>50</v>
       </c>
       <c r="T228" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U228" s="55">
         <v>4</v>
       </c>
       <c r="V228" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W228" s="55">
         <v>8</v>
@@ -46265,10 +46265,10 @@
         <v>1276</v>
       </c>
       <c r="AX228" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY228" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="229" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46324,19 +46324,19 @@
         <v>683</v>
       </c>
       <c r="R229" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S229" s="49">
         <v>50</v>
       </c>
       <c r="T229" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U229" s="55">
         <v>5</v>
       </c>
       <c r="V229" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W229" s="55">
         <v>10</v>
@@ -46420,10 +46420,10 @@
         <v>1276</v>
       </c>
       <c r="AX229" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY229" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="230" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46479,19 +46479,19 @@
         <v>683</v>
       </c>
       <c r="R230" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S230" s="49">
         <v>0</v>
       </c>
       <c r="T230" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U230" s="55">
         <v>0</v>
       </c>
       <c r="V230" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W230" s="55">
         <v>0</v>
@@ -46575,10 +46575,10 @@
         <v>1276</v>
       </c>
       <c r="AX230" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY230" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="231" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46634,19 +46634,19 @@
         <v>683</v>
       </c>
       <c r="R231" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S231" s="49">
         <v>50</v>
       </c>
       <c r="T231" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U231" s="55">
         <v>5</v>
       </c>
       <c r="V231" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W231" s="55">
         <v>10</v>
@@ -46730,10 +46730,10 @@
         <v>1276</v>
       </c>
       <c r="AX231" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY231" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="232" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46789,19 +46789,19 @@
         <v>683</v>
       </c>
       <c r="R232" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S232" s="49">
         <v>50</v>
       </c>
       <c r="T232" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U232" s="55">
         <v>4</v>
       </c>
       <c r="V232" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W232" s="55">
         <v>8</v>
@@ -46885,10 +46885,10 @@
         <v>1276</v>
       </c>
       <c r="AX232" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY232" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="233" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -46944,19 +46944,19 @@
         <v>683</v>
       </c>
       <c r="R233" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S233" s="49">
         <v>40</v>
       </c>
       <c r="T233" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U233" s="55">
         <v>5</v>
       </c>
       <c r="V233" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W233" s="55">
         <v>10</v>
@@ -47040,10 +47040,10 @@
         <v>1276</v>
       </c>
       <c r="AX233" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY233" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="234" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47099,19 +47099,19 @@
         <v>582</v>
       </c>
       <c r="R234" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S234" s="49">
         <v>30</v>
       </c>
       <c r="T234" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U234" s="55">
         <v>4</v>
       </c>
       <c r="V234" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W234" s="55">
         <v>8</v>
@@ -47195,10 +47195,10 @@
         <v>1276</v>
       </c>
       <c r="AX234" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY234" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="235" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47254,19 +47254,19 @@
         <v>582</v>
       </c>
       <c r="R235" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S235" s="49">
         <v>0</v>
       </c>
       <c r="T235" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U235" s="55">
         <v>0</v>
       </c>
       <c r="V235" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W235" s="55">
         <v>0</v>
@@ -47350,10 +47350,10 @@
         <v>1276</v>
       </c>
       <c r="AX235" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY235" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="236" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47409,19 +47409,19 @@
         <v>683</v>
       </c>
       <c r="R236" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S236" s="49">
         <v>0</v>
       </c>
       <c r="T236" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U236" s="55">
         <v>5</v>
       </c>
       <c r="V236" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W236" s="55">
         <v>10</v>
@@ -47505,10 +47505,10 @@
         <v>1276</v>
       </c>
       <c r="AX236" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY236" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="237" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47564,19 +47564,19 @@
         <v>683</v>
       </c>
       <c r="R237" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S237" s="49">
         <v>50</v>
       </c>
       <c r="T237" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U237" s="55">
         <v>5</v>
       </c>
       <c r="V237" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W237" s="55">
         <v>10</v>
@@ -47660,10 +47660,10 @@
         <v>1276</v>
       </c>
       <c r="AX237" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY237" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="238" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47719,19 +47719,19 @@
         <v>683</v>
       </c>
       <c r="R238" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S238" s="49">
         <v>0</v>
       </c>
       <c r="T238" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U238" s="55">
         <v>3</v>
       </c>
       <c r="V238" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W238" s="55">
         <v>6</v>
@@ -47815,10 +47815,10 @@
         <v>1276</v>
       </c>
       <c r="AX238" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY238" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="239" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -47874,19 +47874,19 @@
         <v>683</v>
       </c>
       <c r="R239" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S239" s="49">
         <v>30</v>
       </c>
       <c r="T239" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U239" s="55">
         <v>4</v>
       </c>
       <c r="V239" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W239" s="55">
         <v>8</v>
@@ -47970,10 +47970,10 @@
         <v>1276</v>
       </c>
       <c r="AX239" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY239" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="240" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48029,19 +48029,19 @@
         <v>422</v>
       </c>
       <c r="R240" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S240" s="49">
         <v>0</v>
       </c>
       <c r="T240" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U240" s="55">
         <v>2</v>
       </c>
       <c r="V240" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W240" s="55">
         <v>4</v>
@@ -48125,10 +48125,10 @@
         <v>1276</v>
       </c>
       <c r="AX240" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY240" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="241" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48184,19 +48184,19 @@
         <v>683</v>
       </c>
       <c r="R241" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S241" s="49">
         <v>0</v>
       </c>
       <c r="T241" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U241" s="55">
         <v>0</v>
       </c>
       <c r="V241" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W241" s="55">
         <v>0</v>
@@ -48280,10 +48280,10 @@
         <v>1276</v>
       </c>
       <c r="AX241" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY241" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="242" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48339,19 +48339,19 @@
         <v>683</v>
       </c>
       <c r="R242" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S242" s="49">
         <v>40</v>
       </c>
       <c r="T242" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U242" s="55">
         <v>5</v>
       </c>
       <c r="V242" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W242" s="55">
         <v>10</v>
@@ -48435,10 +48435,10 @@
         <v>1276</v>
       </c>
       <c r="AX242" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY242" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="243" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48494,19 +48494,19 @@
         <v>683</v>
       </c>
       <c r="R243" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S243" s="49">
         <v>30</v>
       </c>
       <c r="T243" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U243" s="55">
         <v>3</v>
       </c>
       <c r="V243" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W243" s="55">
         <v>6</v>
@@ -48590,10 +48590,10 @@
         <v>1276</v>
       </c>
       <c r="AX243" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY243" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="244" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48649,19 +48649,19 @@
         <v>683</v>
       </c>
       <c r="R244" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S244" s="49">
         <v>50</v>
       </c>
       <c r="T244" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U244" s="55">
         <v>5</v>
       </c>
       <c r="V244" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W244" s="55">
         <v>10</v>
@@ -48745,10 +48745,10 @@
         <v>1276</v>
       </c>
       <c r="AX244" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY244" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="245" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48804,19 +48804,19 @@
         <v>683</v>
       </c>
       <c r="R245" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S245" s="49">
         <v>50</v>
       </c>
       <c r="T245" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U245" s="55">
         <v>5</v>
       </c>
       <c r="V245" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W245" s="55">
         <v>10</v>
@@ -48900,10 +48900,10 @@
         <v>1276</v>
       </c>
       <c r="AX245" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY245" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="246" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -48959,19 +48959,19 @@
         <v>683</v>
       </c>
       <c r="R246" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S246" s="49">
         <v>50</v>
       </c>
       <c r="T246" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U246" s="55">
         <v>5</v>
       </c>
       <c r="V246" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W246" s="55">
         <v>10</v>
@@ -49055,10 +49055,10 @@
         <v>1276</v>
       </c>
       <c r="AX246" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY246" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="247" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49114,19 +49114,19 @@
         <v>423</v>
       </c>
       <c r="R247" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S247" s="49">
         <v>0</v>
       </c>
       <c r="T247" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U247" s="55">
         <v>0</v>
       </c>
       <c r="V247" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W247" s="55">
         <v>0</v>
@@ -49210,10 +49210,10 @@
         <v>1276</v>
       </c>
       <c r="AX247" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY247" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="248" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49269,19 +49269,19 @@
         <v>683</v>
       </c>
       <c r="R248" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S248" s="49">
         <v>40</v>
       </c>
       <c r="T248" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U248" s="55">
         <v>4</v>
       </c>
       <c r="V248" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W248" s="55">
         <v>8</v>
@@ -49365,10 +49365,10 @@
         <v>1276</v>
       </c>
       <c r="AX248" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY248" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="249" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49424,19 +49424,19 @@
         <v>582</v>
       </c>
       <c r="R249" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S249" s="49">
         <v>30</v>
       </c>
       <c r="T249" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U249" s="55">
         <v>4</v>
       </c>
       <c r="V249" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W249" s="55">
         <v>8</v>
@@ -49520,10 +49520,10 @@
         <v>1276</v>
       </c>
       <c r="AX249" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY249" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="250" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49579,19 +49579,19 @@
         <v>683</v>
       </c>
       <c r="R250" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S250" s="49">
         <v>40</v>
       </c>
       <c r="T250" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U250" s="55">
         <v>4</v>
       </c>
       <c r="V250" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W250" s="55">
         <v>8</v>
@@ -49675,10 +49675,10 @@
         <v>1276</v>
       </c>
       <c r="AX250" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY250" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="251" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49734,19 +49734,19 @@
         <v>683</v>
       </c>
       <c r="R251" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S251" s="49">
         <v>50</v>
       </c>
       <c r="T251" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U251" s="55">
         <v>5</v>
       </c>
       <c r="V251" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W251" s="55">
         <v>10</v>
@@ -49830,10 +49830,10 @@
         <v>1276</v>
       </c>
       <c r="AX251" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY251" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="252" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -49889,19 +49889,19 @@
         <v>582</v>
       </c>
       <c r="R252" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S252" s="49">
         <v>0</v>
       </c>
       <c r="T252" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U252" s="55">
         <v>0</v>
       </c>
       <c r="V252" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W252" s="55">
         <v>0</v>
@@ -49985,10 +49985,10 @@
         <v>1276</v>
       </c>
       <c r="AX252" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY252" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="253" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50044,19 +50044,19 @@
         <v>683</v>
       </c>
       <c r="R253" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S253" s="49">
         <v>60</v>
       </c>
       <c r="T253" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U253" s="55">
         <v>5</v>
       </c>
       <c r="V253" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W253" s="55">
         <v>10</v>
@@ -50140,10 +50140,10 @@
         <v>1276</v>
       </c>
       <c r="AX253" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY253" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="254" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50199,19 +50199,19 @@
         <v>683</v>
       </c>
       <c r="R254" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S254" s="49">
         <v>50</v>
       </c>
       <c r="T254" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U254" s="55">
         <v>5</v>
       </c>
       <c r="V254" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W254" s="55">
         <v>10</v>
@@ -50295,10 +50295,10 @@
         <v>1276</v>
       </c>
       <c r="AX254" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY254" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="255" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50354,19 +50354,19 @@
         <v>683</v>
       </c>
       <c r="R255" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S255" s="49">
         <v>50</v>
       </c>
       <c r="T255" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U255" s="55">
         <v>5</v>
       </c>
       <c r="V255" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W255" s="55">
         <v>10</v>
@@ -50450,10 +50450,10 @@
         <v>1276</v>
       </c>
       <c r="AX255" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY255" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="256" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50509,19 +50509,19 @@
         <v>683</v>
       </c>
       <c r="R256" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S256" s="49">
         <v>50</v>
       </c>
       <c r="T256" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U256" s="55">
         <v>5</v>
       </c>
       <c r="V256" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W256" s="55">
         <v>10</v>
@@ -50605,10 +50605,10 @@
         <v>1276</v>
       </c>
       <c r="AX256" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY256" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="257" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50664,19 +50664,19 @@
         <v>683</v>
       </c>
       <c r="R257" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S257" s="49">
         <v>30</v>
       </c>
       <c r="T257" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U257" s="55">
         <v>3</v>
       </c>
       <c r="V257" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W257" s="55">
         <v>6</v>
@@ -50760,10 +50760,10 @@
         <v>1276</v>
       </c>
       <c r="AX257" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY257" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="258" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50819,19 +50819,19 @@
         <v>582</v>
       </c>
       <c r="R258" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S258" s="49">
         <v>20</v>
       </c>
       <c r="T258" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U258" s="55">
         <v>0</v>
       </c>
       <c r="V258" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W258" s="55">
         <v>0</v>
@@ -50915,10 +50915,10 @@
         <v>1276</v>
       </c>
       <c r="AX258" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY258" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="259" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -50974,19 +50974,19 @@
         <v>683</v>
       </c>
       <c r="R259" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S259" s="49">
         <v>50</v>
       </c>
       <c r="T259" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U259" s="55">
         <v>5</v>
       </c>
       <c r="V259" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W259" s="55">
         <v>10</v>
@@ -51070,10 +51070,10 @@
         <v>1276</v>
       </c>
       <c r="AX259" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY259" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="260" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51129,19 +51129,19 @@
         <v>683</v>
       </c>
       <c r="R260" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S260" s="49">
         <v>60</v>
       </c>
       <c r="T260" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U260" s="55">
         <v>5</v>
       </c>
       <c r="V260" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W260" s="55">
         <v>10</v>
@@ -51225,10 +51225,10 @@
         <v>1276</v>
       </c>
       <c r="AX260" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY260" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="261" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51284,19 +51284,19 @@
         <v>683</v>
       </c>
       <c r="R261" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S261" s="49">
         <v>30</v>
       </c>
       <c r="T261" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U261" s="55">
         <v>3</v>
       </c>
       <c r="V261" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W261" s="55">
         <v>6</v>
@@ -51380,10 +51380,10 @@
         <v>1276</v>
       </c>
       <c r="AX261" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY261" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="262" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51439,19 +51439,19 @@
         <v>683</v>
       </c>
       <c r="R262" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S262" s="49">
         <v>60</v>
       </c>
       <c r="T262" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U262" s="55">
         <v>6</v>
       </c>
       <c r="V262" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W262" s="55">
         <v>12</v>
@@ -51502,7 +51502,7 @@
         <v>187</v>
       </c>
       <c r="AM262" s="44" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AN262" s="47" t="s">
         <v>588</v>
@@ -51535,10 +51535,10 @@
         <v>1276</v>
       </c>
       <c r="AX262" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY262" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="263" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51594,19 +51594,19 @@
         <v>683</v>
       </c>
       <c r="R263" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S263" s="49">
         <v>30</v>
       </c>
       <c r="T263" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U263" s="55">
         <v>3</v>
       </c>
       <c r="V263" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W263" s="55">
         <v>6</v>
@@ -51690,10 +51690,10 @@
         <v>1276</v>
       </c>
       <c r="AX263" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY263" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="264" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51749,19 +51749,19 @@
         <v>683</v>
       </c>
       <c r="R264" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S264" s="49">
         <v>30</v>
       </c>
       <c r="T264" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U264" s="55">
         <v>3</v>
       </c>
       <c r="V264" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W264" s="55">
         <v>6</v>
@@ -51845,10 +51845,10 @@
         <v>1276</v>
       </c>
       <c r="AX264" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY264" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="265" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -51904,19 +51904,19 @@
         <v>422</v>
       </c>
       <c r="R265" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S265" s="49">
         <v>30</v>
       </c>
       <c r="T265" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U265" s="55">
         <v>3</v>
       </c>
       <c r="V265" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W265" s="55">
         <v>6</v>
@@ -52000,10 +52000,10 @@
         <v>1276</v>
       </c>
       <c r="AX265" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY265" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="266" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52059,19 +52059,19 @@
         <v>683</v>
       </c>
       <c r="R266" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S266" s="49">
         <v>100</v>
       </c>
       <c r="T266" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U266" s="55">
         <v>0</v>
       </c>
       <c r="V266" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W266" s="55">
         <v>0</v>
@@ -52155,10 +52155,10 @@
         <v>1276</v>
       </c>
       <c r="AX266" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY266" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="267" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52214,19 +52214,19 @@
         <v>684</v>
       </c>
       <c r="R267" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S267" s="49">
         <v>0</v>
       </c>
       <c r="T267" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U267" s="55">
         <v>0</v>
       </c>
       <c r="V267" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W267" s="55">
         <v>0</v>
@@ -52310,10 +52310,10 @@
         <v>1276</v>
       </c>
       <c r="AX267" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY267" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="268" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52369,19 +52369,19 @@
         <v>683</v>
       </c>
       <c r="R268" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S268" s="49">
         <v>40</v>
       </c>
       <c r="T268" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U268" s="55">
         <v>4</v>
       </c>
       <c r="V268" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W268" s="55">
         <v>8</v>
@@ -52465,10 +52465,10 @@
         <v>1276</v>
       </c>
       <c r="AX268" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY268" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="269" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52524,19 +52524,19 @@
         <v>683</v>
       </c>
       <c r="R269" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S269" s="49">
         <v>50</v>
       </c>
       <c r="T269" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U269" s="55">
         <v>5</v>
       </c>
       <c r="V269" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W269" s="55">
         <v>10</v>
@@ -52620,10 +52620,10 @@
         <v>1276</v>
       </c>
       <c r="AX269" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY269" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="270" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52679,19 +52679,19 @@
         <v>683</v>
       </c>
       <c r="R270" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S270" s="49">
         <v>60</v>
       </c>
       <c r="T270" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U270" s="55">
         <v>5</v>
       </c>
       <c r="V270" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W270" s="55">
         <v>10</v>
@@ -52775,10 +52775,10 @@
         <v>1276</v>
       </c>
       <c r="AX270" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY270" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="271" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52834,19 +52834,19 @@
         <v>582</v>
       </c>
       <c r="R271" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S271" s="49">
         <v>40</v>
       </c>
       <c r="T271" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U271" s="55">
         <v>4</v>
       </c>
       <c r="V271" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W271" s="55">
         <v>8</v>
@@ -52930,10 +52930,10 @@
         <v>1276</v>
       </c>
       <c r="AX271" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY271" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="272" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -52989,19 +52989,19 @@
         <v>683</v>
       </c>
       <c r="R272" s="46" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="S272" s="49">
         <v>40</v>
       </c>
       <c r="T272" s="67" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U272" s="55">
         <v>4</v>
       </c>
       <c r="V272" s="67" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W272" s="55">
         <v>8</v>
@@ -53085,10 +53085,10 @@
         <v>1276</v>
       </c>
       <c r="AX272" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY272" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="273" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53150,13 +53150,13 @@
         <v>1</v>
       </c>
       <c r="T273" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U273" s="55">
         <v>1</v>
       </c>
       <c r="V273" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W273" s="55">
         <v>2</v>
@@ -53240,10 +53240,10 @@
         <v>1276</v>
       </c>
       <c r="AX273" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY273" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="274" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53305,13 +53305,13 @@
         <v>1</v>
       </c>
       <c r="T274" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U274" s="55">
         <v>1</v>
       </c>
       <c r="V274" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W274" s="55">
         <v>3</v>
@@ -53395,10 +53395,10 @@
         <v>1276</v>
       </c>
       <c r="AX274" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY274" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="275" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53460,13 +53460,13 @@
         <v>1</v>
       </c>
       <c r="T275" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U275" s="55" t="s">
         <v>401</v>
       </c>
       <c r="V275" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W275" s="100" t="s">
         <v>185</v>
@@ -53550,10 +53550,10 @@
         <v>1276</v>
       </c>
       <c r="AX275" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY275" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="276" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53615,13 +53615,13 @@
         <v>1</v>
       </c>
       <c r="T276" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U276" s="55">
         <v>1</v>
       </c>
       <c r="V276" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W276" s="55">
         <v>2</v>
@@ -53705,10 +53705,10 @@
         <v>1276</v>
       </c>
       <c r="AX276" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY276" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="277" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53770,13 +53770,13 @@
         <v>1</v>
       </c>
       <c r="T277" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U277" s="55">
         <v>0</v>
       </c>
       <c r="V277" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W277" s="55">
         <v>0</v>
@@ -53860,10 +53860,10 @@
         <v>1276</v>
       </c>
       <c r="AX277" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY277" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="278" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -53925,13 +53925,13 @@
         <v>1</v>
       </c>
       <c r="T278" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U278" s="55">
         <v>1</v>
       </c>
       <c r="V278" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W278" s="55">
         <v>2</v>
@@ -54015,10 +54015,10 @@
         <v>1276</v>
       </c>
       <c r="AX278" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY278" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="279" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54080,13 +54080,13 @@
         <v>1</v>
       </c>
       <c r="T279" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U279" s="55">
         <v>2</v>
       </c>
       <c r="V279" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W279" s="55">
         <v>3</v>
@@ -54170,10 +54170,10 @@
         <v>1276</v>
       </c>
       <c r="AX279" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY279" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="280" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54235,13 +54235,13 @@
         <v>1</v>
       </c>
       <c r="T280" s="68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="U280" s="55">
         <v>1</v>
       </c>
       <c r="V280" s="68" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="W280" s="55">
         <v>3</v>
@@ -54325,10 +54325,10 @@
         <v>1276</v>
       </c>
       <c r="AX280" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY280" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="281" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54480,10 +54480,10 @@
         <v>1276</v>
       </c>
       <c r="AX281" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY281" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="282" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54635,10 +54635,10 @@
         <v>1276</v>
       </c>
       <c r="AX282" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY282" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="283" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54790,10 +54790,10 @@
         <v>1276</v>
       </c>
       <c r="AX283" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY283" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="284" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -54945,10 +54945,10 @@
         <v>1276</v>
       </c>
       <c r="AX284" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY284" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="285" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55100,10 +55100,10 @@
         <v>1276</v>
       </c>
       <c r="AX285" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY285" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="286" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55255,10 +55255,10 @@
         <v>1276</v>
       </c>
       <c r="AX286" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY286" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="287" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55410,10 +55410,10 @@
         <v>1276</v>
       </c>
       <c r="AX287" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY287" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="288" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55565,10 +55565,10 @@
         <v>1276</v>
       </c>
       <c r="AX288" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY288" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="289" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55720,10 +55720,10 @@
         <v>1276</v>
       </c>
       <c r="AX289" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY289" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="290" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -55875,10 +55875,10 @@
         <v>1276</v>
       </c>
       <c r="AX290" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY290" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="291" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56030,10 +56030,10 @@
         <v>1276</v>
       </c>
       <c r="AX291" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY291" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="292" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56185,10 +56185,10 @@
         <v>1276</v>
       </c>
       <c r="AX292" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY292" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="293" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56340,10 +56340,10 @@
         <v>1276</v>
       </c>
       <c r="AX293" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY293" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="294" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56495,10 +56495,10 @@
         <v>1276</v>
       </c>
       <c r="AX294" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY294" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="295" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56650,10 +56650,10 @@
         <v>1276</v>
       </c>
       <c r="AX295" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY295" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="296" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56805,10 +56805,10 @@
         <v>1276</v>
       </c>
       <c r="AX296" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY296" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="297" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -56960,10 +56960,10 @@
         <v>1276</v>
       </c>
       <c r="AX297" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY297" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="298" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -57115,10 +57115,10 @@
         <v>1276</v>
       </c>
       <c r="AX298" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY298" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="299" spans="1:51" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -57270,10 +57270,10 @@
         <v>1276</v>
       </c>
       <c r="AX299" s="33" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AY299" s="31" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
